--- a/docs/weekly/SLATE_REST_2026_W07.xlsx
+++ b/docs/weekly/SLATE_REST_2026_W07.xlsx
@@ -486,14 +486,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Inputs used (UTC). ESPN game-summary Outs (5 names per team cap, not the official inactives): 2026-10-25T18:36:16Z. Sleeper status overlay (newer Out replaces the NFL row): 2026-10-25T18:36:07+00:00. nflverse depth charts: 2026-10-25T12:30:46Z; nflverse injuries: no timestamp in the feed. Lines: ESPN/DraftKings fetched 2026-10-25T18:36Z (no prices; the per-line last_updated_utc stamps run ahead of the fetch time and their zone is unverified, so no recency claim is made from them). Official inactives: not used (the ESPN feed carries injuries, not the NFL inactive list). Code: git 7d64d93.</t>
+          <t>Inputs used (UTC). ESPN game-summary Outs (5 names per team cap, not the official inactives): 2026-10-25T22:51:57Z. Sleeper status overlay (newer Out replaces the NFL row): 2026-10-25T22:51:46+00:00. nflverse depth charts: 2026-10-25T12:30:46Z; nflverse injuries: no timestamp in the feed. Lines: ESPN/DraftKings fetched 2026-10-25T22:52Z (no prices; the per-line last_updated_utc stamps run ahead of the fetch time and their zone is unverified, so no recency claim is made from them). Official inactives: not used (the ESPN feed carries injuries, not the NFL inactive list). Code: git 6994de5.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Started or finished, excluded from picks: CIN@BAL, CLE@TEN, IND@MIN, MIA@NYJ, NE@CHI, NYG@HOU, PIT@NO, SF@ATL, TB@CAR.</t>
+          <t>Started or finished, excluded from picks: CIN@BAL, CLE@TEN, DEN@ARI, GB@DET, IND@MIN, LA@LV, MIA@NYJ, NE@CHI, NYG@HOU, PIT@NO, SF@ATL, TB@CAR.</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -577,77 +577,77 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>KC@SEA: Noah Gray rec O1.5 + KC@SEA: Sam Darnold pass TD 1+</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.433</v>
+        <v>0.393</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.665</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="E7" t="n">
-        <v>159</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>KC@SEA: Noah Gray rec O1.5 + DAL@PHI: Dak Prescott pass TD 1+</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.433</v>
+        <v>0.381</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.664</v>
+        <v>0.539</v>
       </c>
       <c r="D8" t="n">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="E8" t="n">
-        <v>159</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jared Goff pass TD 1+</t>
+          <t>KC@SEA: Kenneth Walker III rush_yds O79.5 + KC@SEA: Sam Darnold pass TD 1+</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.429</v>
+        <v>0.367</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.655</v>
+        <v>0.509</v>
       </c>
       <c r="D9" t="n">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="E9" t="n">
-        <v>161</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GB@DET: Jordan Love rush_yds U6.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>KC@SEA: Kenneth Walker III rush_yds O79.5 + DAL@PHI: Dak Prescott pass TD 1+</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.418</v>
+        <v>0.362</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.635</v>
+        <v>0.494</v>
       </c>
       <c r="D10" t="n">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="E10" t="n">
-        <v>168</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11"/>
@@ -688,77 +688,77 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
+          <t>KC@SEA: Jaxon Smith-Njigba anytime TD + KC@SEA: Sam Darnold pass TD 1+</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.377</v>
+        <v>0.367</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.476</v>
+        <v>0.45</v>
       </c>
       <c r="D14" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E14" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love pass TD 2+</t>
+          <t>KC@SEA: Kenneth Walker III anytime TD + KC@SEA: Sam Darnold pass TD 1+</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.464</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="E15" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KC@SEA: Kenneth Walker III anytime TD + GB@DET: Jordan Love pass TD 1+</t>
+          <t>KC@SEA: Kenneth Walker III anytime TD + DAL@PHI: Dak Prescott pass TD 1+</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.349</v>
+        <v>0.327</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.453</v>
+        <v>0.41</v>
       </c>
       <c r="D16" t="n">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="E16" t="n">
-        <v>221</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KC@SEA: Kenneth Walker III anytime TD + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>KC@SEA: Kenneth Walker III anytime TD + KC@SEA: Patrick Mahomes pass TD 1+</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.349</v>
+        <v>0.317</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.452</v>
+        <v>0.379</v>
       </c>
       <c r="D17" t="n">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="E17" t="n">
-        <v>221</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18"/>
@@ -806,601 +806,369 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love rush_yds U6.5 + LA@LV: Matthew Stafford pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="D22" t="n">
-        <v>278</v>
-      </c>
-      <c r="E22" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + LA@LV: Kyren Williams rush_att U15.5 + GB@DET: Jordan Love pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="D23" t="n">
-        <v>281</v>
-      </c>
-      <c r="E23" t="n">
-        <v>327</v>
-      </c>
-    </row>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love rush_yds U6.5 + GB@DET: Jared Goff pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>0.262</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="D24" t="n">
-        <v>281</v>
-      </c>
-      <c r="E24" t="n">
-        <v>327</v>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Touchdown-led (at least one TD leg, longer shot)</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + KC@SEA: Noah Gray rec O1.5 + GB@DET: Jordan Love pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="D25" t="n">
-        <v>284</v>
-      </c>
-      <c r="E25" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="26"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Hit probability</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Raw sim</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Fair odds</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Play at or better</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KC@SEA: Noah Gray rec O1.5 + KC@SEA: Jaxon Smith-Njigba anytime TD + KC@SEA: Sam Darnold pass TD 1+</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="D26" t="n">
+        <v>348</v>
+      </c>
+      <c r="E26" t="n">
+        <v>402</v>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Touchdown-led (at least one TD leg, longer shot)</t>
-        </is>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KC@SEA: Emanuel Wilson rush_att O14.5 + KC@SEA: Jaxon Smith-Njigba anytime TD + KC@SEA: Sam Darnold pass TD 1+</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="D27" t="n">
+        <v>385</v>
+      </c>
+      <c r="E27" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Legs</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Hit probability</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Raw sim</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Fair odds</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Play at or better</t>
-        </is>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KC@SEA: Kenneth Walker III rush_yds O79.5 + KC@SEA: Jaxon Smith-Njigba anytime TD + KC@SEA: Sam Darnold pass TD 1+</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="D28" t="n">
+        <v>385</v>
+      </c>
+      <c r="E28" t="n">
+        <v>443</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
+          <t>KC@SEA: Noah Gray rec O1.5 + KC@SEA: Kenneth Walker III anytime TD + KC@SEA: Sam Darnold pass TD 1+</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.239</v>
+        <v>0.205</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0.364</v>
+        <v>0.306</v>
       </c>
       <c r="D29" t="n">
-        <v>319</v>
+        <v>389</v>
       </c>
       <c r="E29" t="n">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>GB@DET: Jordan Love rush_yds U6.5 + GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="D30" t="n">
-        <v>329</v>
-      </c>
-      <c r="E30" t="n">
-        <v>381</v>
-      </c>
-    </row>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LA@LV: Kyren Williams rush_att U15.5 + GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="D31" t="n">
-        <v>338</v>
-      </c>
-      <c r="E31" t="n">
-        <v>390</v>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>4-leg</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>KC@SEA: Noah Gray rec O1.5 + GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="D32" t="n">
-        <v>341</v>
-      </c>
-      <c r="E32" t="n">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Highest chance to hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Hit probability</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Raw sim</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Fair odds</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Play at or better</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>4-leg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Highest chance to hit</t>
-        </is>
-      </c>
-    </row>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35"/>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Touchdown-led (at least one TD leg, longer shot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Legs</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Hit probability</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Raw sim</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Fair odds</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Play at or better</t>
         </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love rush_yds U6.5 + KC@SEA: Noah Gray rec O1.5 + LA@LV: Matthew Stafford pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="D37" t="n">
-        <v>529</v>
-      </c>
-      <c r="E37" t="n">
-        <v>604</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love rush_yds U6.5 + LA@LV: Kyren Williams rush_att U15.5 + GB@DET: Jared Goff pass TD 1+</t>
+          <t>KC@SEA: Noah Gray rec O1.5 + KC@SEA: Kenneth Walker III anytime TD + KC@SEA: Jaxon Smith-Njigba anytime TD + KC@SEA: Sam Darnold pass TD 1+</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.159</v>
+        <v>0.117</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0.342</v>
+        <v>0.174</v>
       </c>
       <c r="D38" t="n">
-        <v>529</v>
+        <v>758</v>
       </c>
       <c r="E38" t="n">
-        <v>605</v>
+        <v>861</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love rush_yds U6.5 + LA@LV: Kyren Williams rush_att U15.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>KC@SEA: Emanuel Wilson rush_att O14.5 + KC@SEA: Kenneth Walker III anytime TD + KC@SEA: Jaxon Smith-Njigba anytime TD + KC@SEA: Sam Darnold pass TD 1+</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.158</v>
+        <v>0.104</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.342</v>
+        <v>0.143</v>
       </c>
       <c r="D39" t="n">
-        <v>533</v>
+        <v>859</v>
       </c>
       <c r="E39" t="n">
-        <v>609</v>
+        <v>974</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + LA@LV: Kyren Williams rush_att U15.5 + KC@SEA: Noah Gray rec O1.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>KC@SEA: Noah Gray rec O1.5 + KC@SEA: Kenneth Walker III anytime TD + KC@SEA: Jaxon Smith-Njigba anytime TD + DAL@PHI: Dak Prescott pass TD 1+</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>0.158</v>
+        <v>0.092</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0.333</v>
+        <v>0.135</v>
       </c>
       <c r="D40" t="n">
-        <v>534</v>
+        <v>992</v>
       </c>
       <c r="E40" t="n">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Touchdown-led (at least one TD leg, longer shot)</t>
-        </is>
-      </c>
-    </row>
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KC@SEA: Noah Gray rec O1.5 + KC@SEA: Kenneth Walker III anytime TD + KC@SEA: Jaxon Smith-Njigba anytime TD + KC@SEA: Patrick Mahomes pass TD 1+</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>0.08900000000000001</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Legs</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Hit probability</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Raw sim</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Fair odds</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Play at or better</t>
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Quarterback passing-TD ladder (calibrated market: the model beat the books here in W4; fair odds)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love rush_yds U6.5 + GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="D44" t="n">
-        <v>578</v>
-      </c>
-      <c r="E44" t="n">
-        <v>659</v>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Raw simulation probability, with the 50/50-shrunk figure used in parlays in brackets. Treat anything above 85% raw as 'very likely', not a number to price. Backup QBs are not listed.</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + LA@LV: Kyren Williams rush_att U15.5 + GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="D45" t="n">
-        <v>591</v>
-      </c>
-      <c r="E45" t="n">
-        <v>674</v>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>1+ raw (shrunk)</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>2+ raw (shrunk)</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DEN@ARI: Tyler Allgeier rec U2.5 + KC@SEA: Noah Gray rec O1.5 + GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="D46" t="n">
-        <v>597</v>
-      </c>
-      <c r="E46" t="n">
-        <v>680</v>
+          <t>Sam Darnold</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>79% (65%)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>44% (47%)</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GB@DET: Jordan Love rush_yds U6.5 + LA@LV: Kyren Williams rush_att U15.5 + GB@DET: Amon-Ra St. Brown anytime TD + GB@DET: Jared Goff pass TD 1+</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="D47" t="n">
-        <v>608</v>
-      </c>
-      <c r="E47" t="n">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Quarterback passing-TD ladder (calibrated market: the model beat the books here in W4; fair odds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Raw simulation probability, with the 50/50-shrunk figure used in parlays in brackets. Treat anything above 85% raw as 'very likely', not a number to price. Backup QBs are not listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>1+ raw (shrunk)</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>2+ raw (shrunk)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Jordan Love</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>87% (68%)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>61% (55%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Matthew Stafford</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>87% (68%)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>56% (53%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Jared Goff</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>85% (68%)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>55% (53%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Kirk Cousins</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>82% (66%)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>48% (49%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Bo Nix</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>80% (65%)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>46% (48%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Sam Darnold</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>78% (64%)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>43% (47%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
           <t>Dak Prescott</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>76% (63%)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>40% (45%)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Jacoby Brissett</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>69% (60%)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>30% (40%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Patrick Mahomes</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>66% (58%)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>30% (40%)</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>68% (59%)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>31% (40%)</t>
         </is>
       </c>
     </row>
@@ -1600,13 +1368,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1620,7 +1388,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>1 players have posted lines but no projection row (not on the 2026 stats universe, injured/exempt, or name mismatch). Nothing is published for them:</t>
+          <t>0 players have posted lines but no projection row (not on the 2026 stats universe, injured/exempt, or name mismatch). Nothing is published for them:</t>
         </is>
       </c>
     </row>
@@ -1646,57 +1414,52 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Withheld on purpose (no line, touchdown or parlay leg):</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Josh Jacobs</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GB@DET</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>reception_yds, receptions, rush_attempts, rush_yds</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Withheld on purpose (no line, touchdown or parlay leg):</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>reason</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RB1 on the depth chart and ACT on the roster with no 2026 games and no projection row (book lines posted; role unknown)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Josh Jacobs</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1706,14 +1469,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RB1 on the depth chart and ACT on the roster with no 2026 games and no projection row (book lines posted; role unknown)</t>
+          <t>GB backfield shares are unpriced while Jacobs is missing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Kaleb Johnson</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1730,7 +1493,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kaleb Johnson</t>
+          <t>Pierre Strong</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1747,7 +1510,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pierre Strong</t>
+          <t>Chris Brooks</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1756,23 +1519,6 @@
         </is>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t>GB backfield shares are unpriced while Jacobs is missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chris Brooks</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
         <is>
           <t>GB backfield shares are unpriced while Jacobs is missing</t>
         </is>
@@ -1891,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1963,240 +1709,154 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 16:05</t>
+          <t>2026-10-25 20:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARI +4.5 / 43.5</t>
+          <t>SEA -3.0 / 43.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DEN 24.0, ARI 19.4</t>
+          <t>KC 20.3, SEA 23.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DEN 63% / ARI 37%</t>
+          <t>KC 41% / SEA 59%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DEN 23.5, ARI 21.1</t>
+          <t>KC 21.6, SEA 24.1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DEN 57%</t>
+          <t>KC 43%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ARI +4.0</t>
+          <t>SEA -3.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 16:25</t>
+          <t>2026-10-26 20:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DET -3.5 / 55.5</t>
+          <t>PHI +4.5 / 43.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GB 26.0, DET 29.5</t>
+          <t>DAL 23.9, PHI 19.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GB 41% / DET 59%</t>
+          <t>DAL 63% / PHI 37%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>55.5</v>
+        <v>43.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>GB 22.9, DET 27.9</t>
+          <t>DAL 23.1, PHI 23.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>GB 36%</t>
+          <t>DAL 48%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DET -4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LA@LV</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-25 16:25</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LV +3.5 / 48.5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LA 26.1, LV 22.5</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LA 61% / LV 39%</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LA 24.7, LV 23.3</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>LA 54%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>LV +4.0</t>
-        </is>
-      </c>
-    </row>
+          <t>PHI +4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KC@SEA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-25 20:20</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SEA -3.0 / 42.5</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>KC 19.8, SEA 22.7</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>KC 41% / SEA 59%</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>KC 21.5, SEA 24.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>KC 43%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>SEA -3.0</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Already played: NE@CHI final NE 24, CHI 30 (market CHI -3.0, total 50.5; projected 23.7-26.7).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-26 20:15</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PHI +4.5 / 43.5</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>DAL 23.8, PHI 19.5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>DAL 62% / PHI 38%</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>DAL 23.0, PHI 23.9</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>DAL 47%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PHI +4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Already played: PIT@NO final PIT 16, NO 10 (market NO +3.0, total 43.5; projected 23.1-20.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Already played: SF@ATL final SF 20, ATL 29 (market ATL +2.5, total 49.5; projected 26.0-23.4).</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Already played: NE@CHI final NE 24, CHI 30 (market CHI -3.0, total 50.5; projected 23.7-26.7).</t>
+          <t>Already played: CIN@BAL final CIN 35, BAL 13 (market BAL +3.0, total 46.5; projected 24.6-21.7).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Already played: PIT@NO final PIT 16, NO 10 (market NO +3.0, total 43.5; projected 23.1-20.2).</t>
+          <t>Already played: TB@CAR final TB 43, CAR 13 (market CAR -3.0, total 44.5; projected 20.8-23.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Already played: NYG@HOU final NYG 27, HOU 21 (market HOU -10.0, total 42.5; projected 16.3-26.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Already played: IND@MIN final IND 10, MIN 16 (market MIN -6.5, total 41.5; projected 17.5-23.9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Already played: MIA@NYJ final MIA 28, NYJ 25 (market NYJ -3.5, total 39.5; projected 17.9-21.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Already played: CLE@TEN final CLE 27, TEN 24 (market TEN +1.5, total 36.5; projected 18.9-17.4).</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -7716,627 +7376,663 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>19.3</v>
       </c>
       <c r="F6" t="n">
-        <v>289.4</v>
+        <v>216.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>12.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>18.4</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="F7" t="n">
-        <v>256.9</v>
+        <v>258</v>
       </c>
       <c r="G7" t="n">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="K7" t="n">
-        <v>11.8</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>16.6</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jared Goff</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>22.2</v>
+        <v>20.7</v>
       </c>
       <c r="F8" t="n">
-        <v>231.4</v>
+        <v>215.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="K8" t="n">
-        <v>11.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>16.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="E9" t="n">
-        <v>18.7</v>
+        <v>19.4</v>
       </c>
       <c r="F9" t="n">
-        <v>213</v>
+        <v>187.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="H9" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="K9" t="n">
-        <v>10.5</v>
+        <v>7.3</v>
       </c>
       <c r="L9" t="n">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Kirk Cousins</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>226.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>14</v>
-      </c>
-    </row>
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>258.3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K11" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>15.7</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Running backs</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sam Darnold</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>13.2</v>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>opp</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>p_active</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>rush_att_mean</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>rush_yds_mean</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>rush_td_mean</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>rec_mean</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>rec_yds_mean</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>rec_td_mean</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>any_td_pct</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>league_ev</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>ppr</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tanner McKee</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>PHI</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DAL</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>20.7</v>
+        <v>13.7</v>
       </c>
       <c r="F13" t="n">
-        <v>215.7</v>
+        <v>54.3</v>
       </c>
       <c r="G13" t="n">
-        <v>1.34</v>
+        <v>0.78</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>2.7</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K13" t="n">
-        <v>8.4</v>
+        <v>17.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>0.6</v>
       </c>
       <c r="L13" t="n">
-        <v>13.8</v>
+        <v>5.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>21.7</v>
+        <v>18.6</v>
       </c>
       <c r="F14" t="n">
-        <v>209.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>0.55</v>
       </c>
       <c r="H14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20</v>
+      </c>
+      <c r="N14" t="n">
         <v>19.7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>13.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dameon Pierce</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>24</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E15" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>187.3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H15" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Running backs</t>
-        </is>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>opp</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>p_active</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>rush_att_mean</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>rush_yds_mean</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>rush_td_mean</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>rec_mean</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>rec_yds_mean</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>rec_td_mean</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>any_td_pct</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>league_ev</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>ppr</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>dk</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saquon Barkley</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>35</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Emari Demercado</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="F19" t="n">
-        <v>92</v>
+        <v>16.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.19</v>
+        <v>0.14</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="I19" t="n">
-        <v>30.8</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.78</v>
+        <v>0.14</v>
       </c>
       <c r="L19" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="M19" t="n">
-        <v>24.8</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>24.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>13.4</v>
+        <v>5.2</v>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>19.3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.65</v>
+        <v>0.09</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="I20" t="n">
-        <v>43.4</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.66</v>
+        <v>0.13</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="M20" t="n">
-        <v>22.9</v>
+        <v>4.9</v>
       </c>
       <c r="N20" t="n">
-        <v>22.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Tyler Goodson</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8353,1344 +8049,1194 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>13.7</v>
+        <v>2.3</v>
       </c>
       <c r="F21" t="n">
-        <v>54.3</v>
+        <v>9.1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.78</v>
+        <v>0.08</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="I21" t="n">
-        <v>17.5</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.6</v>
+        <v>0.11</v>
       </c>
       <c r="L21" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="M21" t="n">
-        <v>15.2</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>15.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Hunter Luepke</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>18.6</v>
+        <v>0.7</v>
       </c>
       <c r="F22" t="n">
-        <v>97.09999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="G22" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="I22" t="n">
-        <v>23.8</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.18</v>
+        <v>0.03</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="L22" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>19.6</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Velus Jones Jr.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>16.2</v>
+        <v>1.9</v>
       </c>
       <c r="F23" t="n">
-        <v>59.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.37</v>
+        <v>0.04</v>
       </c>
       <c r="H23" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>28.9</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.24</v>
+        <v>0.01</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="M23" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>16</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Brady Russell</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>54.9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="I24" t="n">
-        <v>9.1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.43</v>
+        <v>0.01</v>
       </c>
       <c r="L24" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="M24" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N24" t="n">
-        <v>10.7</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Ben VanSumeren</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>SEA</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>KC</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>60.1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="I25" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Dameon Pierce</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F26" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M26" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>13.1</v>
-      </c>
-    </row>
+        <v>0.2</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F27" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I27" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M27" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="N27" t="n">
-        <v>8.800000000000001</v>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Wide receivers</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F28" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N28" t="n">
-        <v>9.6</v>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>opp</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>p_active</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>tgt_mean</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>rec_mean</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>rec_yds_mean</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>rec_td_mean</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>any_td_pct</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>league_ev</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>ppr</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.4</v>
+        <v>11.1</v>
       </c>
       <c r="F29" t="n">
-        <v>23.8</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.16</v>
+        <v>95.5</v>
       </c>
       <c r="H29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>27.6</v>
+        <v>0.58</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.45</v>
       </c>
       <c r="J29" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>0.31</v>
+        <v>3.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20.1</v>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N29" t="n">
-        <v>10.6</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="F30" t="n">
-        <v>59.8</v>
+        <v>6.6</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I30" t="n">
-        <v>10.8</v>
+        <v>0.42</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.35</v>
       </c>
       <c r="J30" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>17.6</v>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N30" t="n">
-        <v>10.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pierre Strong</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E31" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>21.4</v>
+        <v>5.4</v>
       </c>
       <c r="G31" t="n">
-        <v>0.17</v>
+        <v>71.5</v>
       </c>
       <c r="H31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I31" t="n">
-        <v>28.1</v>
+        <v>0.3</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.26</v>
       </c>
       <c r="J31" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>0.28</v>
+        <v>1.7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>14.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>10.4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>SEA</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>KC</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="F32" t="n">
-        <v>28.8</v>
+        <v>4.1</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>44.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I32" t="n">
-        <v>12.1</v>
+        <v>0.27</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.24</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>0.24</v>
+        <v>1.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>10.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sione Vaki</t>
+          <t>Darius Cooper</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>1.6</v>
       </c>
       <c r="G33" t="n">
-        <v>0.18</v>
+        <v>22</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I33" t="n">
-        <v>4.7</v>
+        <v>0.26</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.23</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>0.18</v>
+        <v>1.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
       <c r="D34" s="6" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="F34" t="n">
-        <v>34.7</v>
+        <v>3.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.18</v>
+        <v>39.1</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" t="n">
-        <v>15.2</v>
+        <v>0.24</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0.21</v>
       </c>
       <c r="J34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>0.23</v>
+        <v>1.4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Emari Demercado</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>DAL</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>PHI</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="F35" t="n">
-        <v>16.9</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>0.14</v>
+        <v>43.6</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I35" t="n">
-        <v>3.6</v>
+        <v>0.21</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>0.14</v>
+        <v>1.3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3.4</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bam Knight</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="F36" t="n">
-        <v>31.7</v>
+        <v>2.6</v>
       </c>
       <c r="G36" t="n">
-        <v>0.14</v>
+        <v>30.2</v>
       </c>
       <c r="H36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Rashid Shaheed</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Andrew Armstrong</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J38" t="n">
         <v>0.7</v>
       </c>
-      <c r="I36" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="K38" t="n">
         <v>5.1</v>
       </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>Wide receivers</t>
-        </is>
+      <c r="L38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>opp</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>p_active</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>tgt_mean</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>rec_mean</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>rec_yds_mean</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>rec_td_mean</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>any_td_pct</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>league_ev</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>ppr</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>dk</t>
-        </is>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Marquise Brown</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>21</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>10.4</v>
+        <v>2.2</v>
       </c>
       <c r="F40" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="G40" t="n">
-        <v>67.7</v>
+        <v>15</v>
       </c>
       <c r="H40" t="n">
-        <v>0.64</v>
+        <v>0.09</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>0.48</v>
+        <v>0.09</v>
       </c>
       <c r="J40" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="K40" t="n">
-        <v>17.1</v>
+        <v>3.3</v>
       </c>
       <c r="L40" t="n">
-        <v>17.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F41" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="G41" t="n">
-        <v>74.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6</v>
+        <v>0.08</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.46</v>
+        <v>0.08</v>
       </c>
       <c r="J41" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="K41" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>15.3</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Jonathan Mingo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="G42" t="n">
-        <v>95.90000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.57</v>
+        <v>0.05</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.44</v>
+        <v>0.06</v>
       </c>
       <c r="J42" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="K42" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>20</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Elijah Moore</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>8.6</v>
+        <v>1.3</v>
       </c>
       <c r="F43" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="G43" t="n">
-        <v>89.90000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5</v>
+        <v>0.04</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="J43" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="K43" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>16.4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Cyrus Allen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E44" t="n">
-        <v>10.8</v>
+        <v>1.1</v>
       </c>
       <c r="F44" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="G44" t="n">
-        <v>82.90000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H44" t="n">
-        <v>0.41</v>
+        <v>0.03</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.35</v>
+        <v>0.06</v>
       </c>
       <c r="J44" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="K44" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="L44" t="n">
-        <v>17.5</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Irvin Charles</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E45" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="F45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G45" t="n">
         <v>2.9</v>
       </c>
-      <c r="G45" t="n">
-        <v>39.3</v>
-      </c>
       <c r="H45" t="n">
-        <v>0.34</v>
+        <v>0.01</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.29</v>
+        <v>0.01</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="K45" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L45" t="n">
-        <v>8.9</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Britain Covey</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
         <v>0.95</v>
       </c>
       <c r="E46" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="G46" t="n">
-        <v>52.5</v>
+        <v>2.8</v>
       </c>
       <c r="H46" t="n">
-        <v>0.32</v>
+        <v>0.01</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.29</v>
+        <v>0.01</v>
       </c>
       <c r="J46" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="K46" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L46" t="n">
-        <v>10.7</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Nikko Remigio</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>10.8</v>
+        <v>0.1</v>
       </c>
       <c r="F47" t="n">
-        <v>7.1</v>
+        <v>0.1</v>
       </c>
       <c r="G47" t="n">
-        <v>91.40000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>20</v>
-      </c>
-      <c r="L47" t="n">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>George Pickens</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E48" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="F48" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G48" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K48" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="L48" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
+        <v>0.2</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48"/>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Tre Tucker</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G49" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K49" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L49" t="n">
-        <v>9.6</v>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Tight ends</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Michael Wilson</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G50" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I50" s="6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K50" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L50" t="n">
-        <v>11.1</v>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>opp</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>p_active</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>tgt_mean</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>rec_mean</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>rec_yds_mean</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>rec_td_mean</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>any_td_pct</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>league_ev</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>ppr</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>dk</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Darius Cooper</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9704,257 +9250,257 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E51" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="G51" t="n">
-        <v>21.9</v>
+        <v>55.3</v>
       </c>
       <c r="H51" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="J51" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K51" t="n">
-        <v>5.3</v>
+        <v>12.9</v>
       </c>
       <c r="L51" t="n">
-        <v>5.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>KC</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>SEA</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="F52" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="G52" t="n">
-        <v>43.5</v>
+        <v>29.2</v>
       </c>
       <c r="H52" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="J52" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K52" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="L52" t="n">
-        <v>9.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="E53" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="F53" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="G53" t="n">
-        <v>47.9</v>
+        <v>55.3</v>
       </c>
       <c r="H53" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="J53" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K53" t="n">
-        <v>9.6</v>
+        <v>12.7</v>
       </c>
       <c r="L53" t="n">
-        <v>9.6</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Zach Ertz</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>DAL</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>PHI</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F54" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G54" t="n">
-        <v>39.4</v>
+        <v>37.7</v>
       </c>
       <c r="H54" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J54" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K54" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Makai Lemon</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>PHI</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>DAL</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="G55" t="n">
-        <v>43.6</v>
+        <v>32.9</v>
       </c>
       <c r="H55" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J55" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K55" t="n">
-        <v>9.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="L55" t="n">
-        <v>9.699999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cooper Kupp</t>
+          <t>Noah Gray</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>SEA</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>KC</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="F56" t="n">
         <v>2.6</v>
       </c>
       <c r="G56" t="n">
-        <v>30.2</v>
+        <v>23.8</v>
       </c>
       <c r="H56" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="L56" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Eric Saubert</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9968,988 +9514,204 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="F57" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="G57" t="n">
-        <v>32.5</v>
+        <v>4</v>
       </c>
       <c r="H57" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="K57" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L57" t="n">
-        <v>7</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Konata Mumpfield</t>
+          <t>Brevyn Spann-Ford</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="F58" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="G58" t="n">
-        <v>27.4</v>
+        <v>10.7</v>
       </c>
       <c r="H58" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K58" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L58" t="n">
-        <v>5.6</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Johnny Mundt</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="F59" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="G59" t="n">
-        <v>21.2</v>
+        <v>8.5</v>
       </c>
       <c r="H59" t="n">
-        <v>0.17</v>
+        <v>0.04</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K59" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L59" t="n">
-        <v>4.7</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kendrick Bourne</t>
+          <t>Luke Schoonmaker</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="F60" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="G60" t="n">
-        <v>31.9</v>
+        <v>5.6</v>
       </c>
       <c r="H60" t="n">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K60" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="L60" t="n">
-        <v>7</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cody White</t>
+          <t>Jake Briningstool</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="F61" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="G61" t="n">
-        <v>16.2</v>
+        <v>4.7</v>
       </c>
       <c r="H61" t="n">
-        <v>0.16</v>
+        <v>0.02</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K61" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L61" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Troy Franklin</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G62" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I62" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L62" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
+        <v>1.1</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+    </row>
+    <row r="62"/>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Jalen Nailor</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G63" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I63" s="6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K63" t="n">
-        <v>5</v>
-      </c>
-      <c r="L63" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>Tight ends</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>opp</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>p_active</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>tgt_mean</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>rec_mean</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>rec_yds_mean</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>rec_td_mean</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>any_td_pct</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>league_ev</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>ppr</t>
-        </is>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>dk</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Sam LaPorta</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>8</v>
-      </c>
-      <c r="F67" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G67" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I67" s="6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K67" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L67" t="n">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Tucker Kraft</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F68" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G68" t="n">
-        <v>57</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="I68" s="6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J68" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K68" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L68" t="n">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Brock Bowers</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E69" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F69" t="n">
-        <v>6</v>
-      </c>
-      <c r="G69" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I69" s="6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K69" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="L69" t="n">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Colby Parkinson</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E70" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F70" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I70" s="6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K70" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="L70" t="n">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Trey McBride</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F71" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G71" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I71" s="6" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K71" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="L71" t="n">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Tyler Higbee</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F72" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G72" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I72" s="6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J72" t="n">
-        <v>2</v>
-      </c>
-      <c r="K72" t="n">
-        <v>12</v>
-      </c>
-      <c r="L72" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Dallas Goedert</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E73" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F73" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G73" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I73" s="6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="L73" t="n">
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>AJ Barner</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F74" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G74" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I74" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J74" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K74" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="L74" t="n">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Travis Kelce</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E75" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F75" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G75" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I75" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J75" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K75" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L75" t="n">
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Zach Ertz</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="F76" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G76" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I76" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J76" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K76" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L76" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Michael Mayer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>LV</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>LA</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F77" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G77" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I77" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J77" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K77" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L77" t="n">
-        <v>8.300000000000001</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Evan Engram</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G78" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I78" s="6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J78" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K78" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L78" t="n">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Jake Ferguson</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F79" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G79" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I79" s="6" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J79" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K79" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L79" t="n">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Noah Gray</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F80" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G80" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I80" s="6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K80" t="n">
-        <v>6</v>
-      </c>
-      <c r="L80" t="n">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Kickers (this league: FG 3, XP 1; ranked by team implied points, the only validated signal; differences are within noise): DET 8.3; HOU 7.8; LA 7.8; SF 7.8; GB 7.8; CIN 7.6; DEN 7.5; MIN 7.5; DAL 7.5; CAR 7.5</t>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Kickers (this league: FG 3, XP 1; ranked by team implied points, the only validated signal; differences are within noise): DET 8.3; LA 7.9; GB 7.8; DEN 7.6; DAL 7.5; SEA 7.4; LV 7.4; KC 7.0; ARI 7.0; PHI 6.9</t>
         </is>
       </c>
     </row>
@@ -10970,7 +9732,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -11049,17 +9811,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11068,36 +9830,40 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.778</v>
+        <v>0.602</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.778</v>
+        <v>0.602</v>
       </c>
       <c r="G5" t="n">
-        <v>-350</v>
+        <v>-151</v>
       </c>
       <c r="H5" t="n">
-        <v>-227</v>
+        <v>-116</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>opp QB: fill-in QB (Tanner McKee) red-team downgrade</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11106,16 +9872,16 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.6559999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.6559999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="G6" t="n">
-        <v>-191</v>
+        <v>-118</v>
       </c>
       <c r="H6" t="n">
-        <v>-141</v>
+        <v>107</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>1</v>
@@ -11125,77 +9891,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.6</v>
+        <v>0.453</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.6</v>
+        <v>0.453</v>
       </c>
       <c r="G7" t="n">
-        <v>-150</v>
+        <v>121</v>
       </c>
       <c r="H7" t="n">
-        <v>-115</v>
+        <v>147</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>opp QB: fill-in QB (Tanner McKee) red-team downgrade</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.525</v>
+        <v>0.421</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.525</v>
+        <v>0.421</v>
       </c>
       <c r="G8" t="n">
-        <v>-110</v>
+        <v>138</v>
       </c>
       <c r="H8" t="n">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>1</v>
@@ -11205,169 +9967,181 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.479</v>
+        <v>0.366</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.479</v>
+        <v>0.366</v>
       </c>
       <c r="G9" t="n">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="H9" t="n">
-        <v>134</v>
+        <v>206</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.461</v>
+        <v>0.351</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.461</v>
+        <v>0.351</v>
       </c>
       <c r="G10" t="n">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="H10" t="n">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.444</v>
+        <v>0.293</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.444</v>
+        <v>0.278</v>
       </c>
       <c r="G11" t="n">
-        <v>125</v>
+        <v>241</v>
       </c>
       <c r="H11" t="n">
-        <v>152</v>
+        <v>282</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.462</v>
+        <v>0.264</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.442</v>
+        <v>0.264</v>
       </c>
       <c r="G12" t="n">
-        <v>117</v>
+        <v>279</v>
       </c>
       <c r="H12" t="n">
-        <v>143</v>
+        <v>325</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11376,16 +10150,16 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.257</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.257</v>
       </c>
       <c r="G13" t="n">
-        <v>132</v>
+        <v>289</v>
       </c>
       <c r="H13" t="n">
-        <v>159</v>
+        <v>336</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>1</v>
@@ -11395,55 +10169,59 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.409</v>
+        <v>0.264</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.409</v>
+        <v>0.25</v>
       </c>
       <c r="G14" t="n">
-        <v>145</v>
+        <v>279</v>
       </c>
       <c r="H14" t="n">
-        <v>174</v>
+        <v>324</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11452,36 +10230,36 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.385</v>
+        <v>0.258</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.385</v>
+        <v>0.247</v>
       </c>
       <c r="G15" t="n">
-        <v>160</v>
+        <v>287</v>
       </c>
       <c r="H15" t="n">
-        <v>191</v>
+        <v>334</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11490,252 +10268,264 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.402</v>
+        <v>0.237</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.385</v>
+        <v>0.237</v>
       </c>
       <c r="G16" t="n">
-        <v>149</v>
+        <v>322</v>
       </c>
       <c r="H16" t="n">
-        <v>179</v>
+        <v>373</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Darius Cooper</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.376</v>
+        <v>0.227</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.376</v>
+        <v>0.227</v>
       </c>
       <c r="G17" t="n">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="H17" t="n">
-        <v>198</v>
+        <v>393</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dameon Pierce</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.371</v>
+        <v>0.215</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.371</v>
+        <v>0.215</v>
       </c>
       <c r="G18" t="n">
-        <v>170</v>
+        <v>366</v>
       </c>
       <c r="H18" t="n">
-        <v>202</v>
+        <v>422</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fill-in QB (Tanner McKee)</t>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Zach Ertz</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>DAL</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.35</v>
+        <v>0.205</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.35</v>
+        <v>0.205</v>
       </c>
       <c r="G19" t="n">
-        <v>186</v>
+        <v>388</v>
       </c>
       <c r="H19" t="n">
-        <v>220</v>
+        <v>446</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>opp QB: fill-in QB (Tanner McKee)</t>
+          <t>fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brock Bowers</t>
+          <t>Makai Lemon</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.365</v>
+        <v>0.196</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.346</v>
+        <v>0.196</v>
       </c>
       <c r="G20" t="n">
-        <v>174</v>
+        <v>409</v>
       </c>
       <c r="H20" t="n">
-        <v>206</v>
+        <v>470</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.346</v>
+        <v>0.172</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.346</v>
+        <v>0.172</v>
       </c>
       <c r="G21" t="n">
-        <v>189</v>
+        <v>480</v>
       </c>
       <c r="H21" t="n">
-        <v>224</v>
+        <v>549</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.322</v>
+        <v>0.167</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.322</v>
+        <v>0.167</v>
       </c>
       <c r="G22" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="H22" t="n">
-        <v>247</v>
+        <v>572</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>1</v>
@@ -11745,35 +10535,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colby Parkinson</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.34</v>
+        <v>0.176</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.322</v>
+        <v>0.167</v>
       </c>
       <c r="G23" t="n">
-        <v>194</v>
+        <v>469</v>
       </c>
       <c r="H23" t="n">
-        <v>229</v>
+        <v>537</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0.95</v>
@@ -11783,17 +10573,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -11802,54 +10592,58 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.309</v>
+        <v>0.232</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.309</v>
+        <v>0.164</v>
       </c>
       <c r="G24" t="n">
-        <v>224</v>
+        <v>331</v>
       </c>
       <c r="H24" t="n">
-        <v>263</v>
+        <v>382</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>0.71</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Noah Gray</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.3</v>
+        <v>0.148</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.3</v>
+        <v>0.148</v>
       </c>
       <c r="G25" t="n">
-        <v>233</v>
+        <v>574</v>
       </c>
       <c r="H25" t="n">
-        <v>273</v>
+        <v>655</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
@@ -11859,191 +10653,199 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.292</v>
+        <v>0.143</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.292</v>
+        <v>0.143</v>
       </c>
       <c r="G26" t="n">
-        <v>242</v>
+        <v>600</v>
       </c>
       <c r="H26" t="n">
-        <v>283</v>
+        <v>684</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Emari Demercado</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.29</v>
+        <v>0.141</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.29</v>
+        <v>0.141</v>
       </c>
       <c r="G27" t="n">
-        <v>244</v>
+        <v>607</v>
       </c>
       <c r="H27" t="n">
-        <v>286</v>
+        <v>692</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.295</v>
+        <v>0.133</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.28</v>
+        <v>0.133</v>
       </c>
       <c r="G28" t="n">
-        <v>239</v>
+        <v>651</v>
       </c>
       <c r="H28" t="n">
-        <v>279</v>
+        <v>741</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Tyler Goodson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.286</v>
+        <v>0.106</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.271</v>
+        <v>0.106</v>
       </c>
       <c r="G29" t="n">
-        <v>250</v>
+        <v>843</v>
       </c>
       <c r="H29" t="n">
-        <v>292</v>
+        <v>956</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Andrew Armstrong</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.255</v>
+        <v>0.106</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.255</v>
+        <v>0.106</v>
       </c>
       <c r="G30" t="n">
-        <v>292</v>
+        <v>845</v>
       </c>
       <c r="H30" t="n">
-        <v>339</v>
+        <v>958</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>1</v>
@@ -12053,59 +10855,55 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.268</v>
+        <v>0.107</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.254</v>
+        <v>0.105</v>
       </c>
       <c r="G31" t="n">
-        <v>273</v>
+        <v>831</v>
       </c>
       <c r="H31" t="n">
-        <v>318</v>
+        <v>943</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>opp QB: fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Marquise Brown</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12114,26 +10912,30 @@
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.249</v>
+        <v>0.094</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.249</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>302</v>
+        <v>969</v>
       </c>
       <c r="H32" t="n">
-        <v>350</v>
+        <v>1098</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -12148,20 +10950,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.244</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.244</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>310</v>
+        <v>1066</v>
       </c>
       <c r="H33" t="n">
-        <v>359</v>
+        <v>1206</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>1</v>
@@ -12171,17 +10973,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -12190,16 +10992,16 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.24</v>
+        <v>0.077</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.24</v>
+        <v>0.077</v>
       </c>
       <c r="G34" t="n">
-        <v>317</v>
+        <v>1205</v>
       </c>
       <c r="H34" t="n">
-        <v>367</v>
+        <v>1362</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>1</v>
@@ -12244,191 +11046,191 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0.421</v>
+        <v>0.221</v>
       </c>
       <c r="E38" t="n">
-        <v>137</v>
+        <v>353</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.265</v>
+        <v>0.164</v>
       </c>
       <c r="E39" t="n">
-        <v>277</v>
+        <v>511</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.217</v>
+        <v>0.114</v>
       </c>
       <c r="E40" t="n">
-        <v>361</v>
+        <v>780</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="D41" s="6" t="n">
-        <v>0.157</v>
+        <v>0.098</v>
       </c>
       <c r="E41" t="n">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.132</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>655</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.121</v>
+        <v>0.067</v>
       </c>
       <c r="E43" t="n">
-        <v>728</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.118</v>
+        <v>0.043</v>
       </c>
       <c r="E44" t="n">
-        <v>747</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.115</v>
+        <v>0.036</v>
       </c>
       <c r="E45" t="n">
-        <v>767</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12442,33 +11244,33 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.109</v>
+        <v>0.034</v>
       </c>
       <c r="E46" t="n">
-        <v>814</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.105</v>
+        <v>0.034</v>
       </c>
       <c r="E47" t="n">
-        <v>853</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="48"/>
@@ -12509,238 +11311,238 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.219</v>
+        <v>0.178</v>
       </c>
       <c r="E51" t="n">
-        <v>358</v>
+        <v>461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.185</v>
+        <v>0.161</v>
       </c>
       <c r="E52" t="n">
-        <v>440</v>
+        <v>523</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.177</v>
+        <v>0.127</v>
       </c>
       <c r="E53" t="n">
-        <v>464</v>
+        <v>686</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="D54" s="6" t="n">
-        <v>0.16</v>
+        <v>0.116</v>
       </c>
       <c r="E54" t="n">
-        <v>525</v>
+        <v>759</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.128</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>681</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>0.121</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>726</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>0.117</v>
+        <v>0.068</v>
       </c>
       <c r="E57" t="n">
-        <v>753</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>0.108</v>
+        <v>0.066</v>
       </c>
       <c r="E58" t="n">
-        <v>822</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>0.108</v>
+        <v>0.064</v>
       </c>
       <c r="E59" t="n">
-        <v>823</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>0.098</v>
+        <v>0.063</v>
       </c>
       <c r="E60" t="n">
-        <v>922</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Sneaky longshots (8% to 25% anytime, active 90%+): Tre Tucker (LV) 25% fair +302, take at +350+; George Holani (SEA) 24% fair +310, take at +359+; Michael Wilson (ARI) 24% fair +317, take at +367+; Travis Kelce (KC) 25% fair +304, take at +353+; Darius Cooper (PHI) 23% fair +333, take at +385+; Xavier Worthy (KC) 22% fair +346, take at +400+; Jameson Williams (DET) 22% fair +356, take at +410+; Ryan Flournoy (DAL) 22% fair +361, take at +417+; Zach Ertz (PHI) 21% fair +378, take at +435+; Bo Nix (DEN) 20% fair +399, take at +459+; Michael Mayer (LV) 20% fair +400, take at +460+; Makai Lemon (PHI) 20% fair +406, take at +466+; Evan Engram (DEN) 19% fair +422, take at +485+; Sione Vaki (DET) 18% fair +443, take at +509+; Jake Ferguson (DAL) 18% fair +452, take at +519+; Cooper Kupp (SEA) 16% fair +516, take at +590+; Rashid Shaheed (SEA) 17% fair +490, take at +561+; Kendrick Bourne (ARI) 15% fair +550, take at +628+; Konata Mumpfield (LA) 15% fair +552, take at +631+; Jacoby Brissett (ARI) 15% fair +555, take at +633+</t>
+          <t>Sneaky longshots (8% to 25% anytime, active 90%+): Xavier Worthy (KC) 24% fair +322, take at +373+; Darius Cooper (PHI) 23% fair +340, take at +393+; Ryan Flournoy (DAL) 21% fair +366, take at +422+; Zach Ertz (PHI) 20% fair +388, take at +446+; Makai Lemon (PHI) 20% fair +409, take at +470+; Jake Ferguson (DAL) 17% fair +480, take at +549+; Cooper Kupp (SEA) 17% fair +500, take at +572+; Rashid Shaheed (SEA) 18% fair +469, take at +537+; Noah Gray (KC) 15% fair +574, take at +655+; Dak Prescott (DAL) 14% fair +600, take at +684+; Emari Demercado (DAL) 14% fair +607, take at +692+; Emmett Johnson (KC) 13% fair +651, take at +741+; Tyler Goodson (DAL) 11% fair +843, take at +956+; Andrew Armstrong (KC) 11% fair +845, take at +958+; Patrick Mahomes (KC) 11% fair +831, take at +943+; Marquise Brown (PHI) 9% fair +969, take at +1098+; Tory Horton (SEA) 9% fair +1066, take at +1206+</t>
         </is>
       </c>
     </row>
@@ -12755,7 +11557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12784,7 +11586,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>187 lines screened: 8 PLAY (3 receiving, tagged thin: W6 receiving lines hit 35 to 52 percent, Thursday 7 of 11), 22 LEAN (the 22 best shown). Pulled by rule: receiving LEANs, pass-volume UNDERs, UNDERs on a teammate of a player now Out or Questionable ('role change'). PLAY = shrunk probability about 55.4%+ (about 61% raw), active 95%+, side cleared in at least half of the player's games. 'Agree' = the model-only track picks the same side.</t>
+          <t>74 lines screened: 2 PLAY (1 receiving, tagged thin: W6 receiving lines hit 35 to 52 percent, Thursday 7 of 11), 12 LEAN (the 12 best shown). Pulled by rule: receiving LEANs, pass-volume UNDERs, UNDERs on a teammate of a player now Out or Questionable ('role change'). PLAY = shrunk probability about 55.4%+ (about 61% raw), active 95%+, side cleared in at least half of the player's games. 'Agree' = the model-only track picks the same side.</t>
         </is>
       </c>
     </row>
@@ -12863,12 +11665,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Noah Gray</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -12878,24 +11680,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="n">
-        <v>-173</v>
+        <v>-153</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -12914,12 +11716,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12929,20 +11731,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.5</v>
+        <v>79.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-166</v>
+        <v>-135</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -12960,22 +11762,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -12984,20 +11786,20 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15.5</v>
+        <v>70.5</v>
       </c>
       <c r="G7" s="6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>0.71</v>
       </c>
-      <c r="H7" s="6" t="n">
-        <v>0.61</v>
-      </c>
       <c r="I7" t="n">
-        <v>-154</v>
+        <v>-244</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -13005,50 +11807,58 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Noah Gray</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>16.5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="I8" t="n">
-        <v>-151</v>
+        <v>-174</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -13056,28 +11866,36 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -13086,20 +11904,20 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-136</v>
+        <v>-153</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13107,23 +11925,31 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13133,24 +11959,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I10" t="n">
-        <v>-130</v>
+        <v>-153</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13158,23 +11984,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13184,24 +12014,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>64.5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I11" t="n">
-        <v>-129</v>
+        <v>-152</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -13209,28 +12039,36 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>pass_cmp</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -13239,20 +12077,20 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>80.5</v>
+        <v>19.5</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="I12" t="n">
-        <v>-129</v>
+        <v>-143</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -13260,8 +12098,16 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13276,34 +12122,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>pass_yds</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>70.5</v>
+        <v>196.5</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.92</v>
+        <v>0.63</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="I13" t="n">
-        <v>-245</v>
+        <v>-131</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -13330,17 +12176,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>pass_cmp</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -13349,20 +12195,20 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>31.5</v>
+        <v>23.5</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="I14" t="n">
-        <v>-204</v>
+        <v>-123</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -13372,10 +12218,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>model vs own record</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13385,12 +12235,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13400,24 +12250,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.77</v>
+        <v>0.58</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="I15" t="n">
-        <v>-175</v>
+        <v>-117</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -13425,16 +12275,8 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13444,17 +12286,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>pass_att</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -13463,20 +12305,20 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7.5</v>
+        <v>37.5</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="I16" t="n">
-        <v>-165</v>
+        <v>-113</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -13486,10 +12328,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>red-team downgrade</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13499,17 +12345,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>pass_att</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -13518,33 +12364,37 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8.5</v>
+        <v>33.5</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="I17" t="n">
-        <v>-155</v>
+        <v>-109</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>red-team downgrade</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13559,7 +12409,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -13573,20 +12423,20 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.71</v>
+        <v>0.52</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="I18" t="n">
-        <v>-152</v>
+        <v>-105</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -13600,894 +12450,6 @@
         </is>
       </c>
       <c r="M18" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-151</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tanner McKee</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>pass_cmp</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-146</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>GB@DET</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sione Vaki</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-144</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>red-team downgrade</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LA@LV</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-137</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>red-team downgrade</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tanner McKee</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>pass_yds</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>193.5</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-137</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LA@LV</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ashton Jeanty</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-130</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>red-team downgrade</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>DEN@ARI</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>RJ Harvey</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-129</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>red-team downgrade</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>pass_cmp</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-123</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>GB@DET</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Jahmyr Gibbs</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-120</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LA@LV</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Matthew Stafford</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>pass_cmp</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-118</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>GB@DET</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Jared Goff</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-118</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>GB@DET</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Jordan Love</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-116</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>KC@SEA</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Emanuel Wilson</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-116</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>pass_att</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-113</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Tanner McKee</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>pass_att</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-109</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tanner McKee</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-105</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
         <is>
           <t>fill-in QB (Tanner McKee)</t>
         </is>
